--- a/docs/management/studhk_timetracking.xlsx
+++ b/docs/management/studhk_timetracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SForm\Nextcloud\forschung\reveald\git\docs\management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D87016-6F3B-4325-A8E3-CDD8EACA47BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49468DA8-1FCA-43D4-B3CF-D2C24DC223EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23130" yWindow="4905" windowWidth="14400" windowHeight="8715" xr2:uid="{97480CD0-13F4-4331-AF6D-2DA589073085}"/>
   </bookViews>
@@ -460,11 +460,11 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C2" s="2">
-        <v>0.66666666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D2" s="2">
         <f>C2-B2</f>
-        <v>8.3333333333333259E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -579,7 +579,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="4">
         <f>SUM(D2:D20)</f>
-        <v>8.3333333333333259E-2</v>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
